--- a/data/trans_camb/P2A_lim_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,89</t>
+          <t>-0,07; 4,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,59</t>
+          <t>-0,32; 4,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 8,67</t>
+          <t>0,69; 8,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,77</t>
+          <t>-0,98; 4,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,85</t>
+          <t>-3,84; 0,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,95</t>
+          <t>1,33; 10,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,8</t>
+          <t>0,23; 3,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,99</t>
+          <t>-1,5; 1,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,65</t>
+          <t>1,86; 7,76</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 390,97</t>
+          <t>-8,05; 368,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 332,57</t>
+          <t>-16,18; 367,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 673,16</t>
+          <t>11,1; 628,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,27; 168,65</t>
+          <t>-22,48; 163,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,57; 32,25</t>
+          <t>-71,39; 34,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,21; 342,47</t>
+          <t>17,79; 354,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 165,03</t>
+          <t>3,39; 176,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,34; 85,88</t>
+          <t>-40,15; 77,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,88; 309,49</t>
+          <t>46,41; 318,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,22</t>
+          <t>0,54; 5,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,46</t>
+          <t>-1,54; 2,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 13,36</t>
+          <t>4,07; 12,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,81</t>
+          <t>0,74; 5,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,44</t>
+          <t>-1,4; 2,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,96</t>
+          <t>-0,06; 6,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,61</t>
+          <t>1,19; 4,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,18</t>
+          <t>-0,99; 1,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,0</t>
+          <t>2,56; 8,07</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,55; 224,91</t>
+          <t>12,23; 201,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 105,88</t>
+          <t>-37,09; 107,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108,43; 501,24</t>
+          <t>88,78; 489,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 250,46</t>
+          <t>14,64; 248,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,08; 111,83</t>
+          <t>-35,12; 126,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 240,79</t>
+          <t>-2,59; 284,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,3; 177,71</t>
+          <t>27,75; 174,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 83,17</t>
+          <t>-26,35; 74,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,15; 282,62</t>
+          <t>64,64; 287,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 5,11</t>
+          <t>-0,54; 5,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,03</t>
+          <t>-3,11; 1,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,45</t>
+          <t>-2,02; 3,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 6,16</t>
+          <t>0,53; 6,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,71</t>
+          <t>-3,18; 1,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,56</t>
+          <t>-1,33; 4,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,94</t>
+          <t>0,85; 4,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,06</t>
+          <t>-2,51; 1,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,13</t>
+          <t>-0,73; 3,31</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 147,94</t>
+          <t>-10,05; 129,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 57,64</t>
+          <t>-47,35; 54,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,5; 94,17</t>
+          <t>-33,28; 98,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,84; 130,05</t>
+          <t>5,71; 128,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,91; 37,29</t>
+          <t>-42,02; 40,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 91,69</t>
+          <t>-17,79; 90,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,68; 107,31</t>
+          <t>11,85; 99,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 23,98</t>
+          <t>-37,79; 21,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 64,33</t>
+          <t>-11,28; 71,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,78</t>
+          <t>-0,95; 5,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,41</t>
+          <t>-0,25; 6,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 8,66</t>
+          <t>-3,52; 8,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 5,59</t>
+          <t>-2,23; 5,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 0,84</t>
+          <t>-6,27; 0,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 4,3</t>
+          <t>-2,25; 4,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,99</t>
+          <t>-0,35; 4,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,59</t>
+          <t>-2,31; 2,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 5,39</t>
+          <t>-2,98; 5,33</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 110,28</t>
+          <t>-11,71; 109,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 126,59</t>
+          <t>-3,48; 118,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,37; 138,21</t>
+          <t>-41,91; 144,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 63,36</t>
+          <t>-17,28; 64,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 10,45</t>
+          <t>-48,12; 12,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 48,39</t>
+          <t>-17,06; 48,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 62,89</t>
+          <t>-4,29; 64,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 34,7</t>
+          <t>-22,47; 33,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 67,21</t>
+          <t>-26,57; 66,29</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,53</t>
+          <t>-3,82; 5,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 2,68</t>
+          <t>-6,39; 2,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,11</t>
+          <t>1,52; 10,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 8,96</t>
+          <t>-0,25; 9,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 9,44</t>
+          <t>0,21; 9,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 6,37</t>
+          <t>-1,12; 6,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 5,92</t>
+          <t>-0,6; 6,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 5,2</t>
+          <t>-1,41; 4,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,4</t>
+          <t>1,56; 7,44</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,83; 55,39</t>
+          <t>-26,63; 54,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,56; 27,01</t>
+          <t>-41,76; 29,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12,68; 114,57</t>
+          <t>8,88; 107,6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 114,18</t>
+          <t>-2,36; 118,63</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 122,38</t>
+          <t>1,63; 115,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 87,7</t>
+          <t>-9,83; 84,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 63,27</t>
+          <t>-4,39; 61,72</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 56,25</t>
+          <t>-11,73; 53,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,63; 79,33</t>
+          <t>12,08; 79,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 9,94</t>
+          <t>-1,73; 9,65</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 2,98</t>
+          <t>-6,81; 2,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 9,6</t>
+          <t>0,29; 9,47</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 7,51</t>
+          <t>-1,89; 8,01</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 5,4</t>
+          <t>-3,48; 5,81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,34; 67,34</t>
+          <t>5,5; 67,71</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 7,22</t>
+          <t>-0,82; 7,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,75</t>
+          <t>-3,83; 2,95</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,01; 53,93</t>
+          <t>4,84; 53,52</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 106,61</t>
+          <t>-12,25; 101,98</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-46,12; 32,43</t>
+          <t>-49,12; 30,55</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 102,35</t>
+          <t>-0,05; 102,66</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 81,5</t>
+          <t>-15,79; 93,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 61,24</t>
+          <t>-27,09; 66,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44,28; 785,38</t>
+          <t>44,34; 764,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 76,02</t>
+          <t>-6,61; 72,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-30,81; 28,27</t>
+          <t>-28,63; 30,39</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42,69; 553,46</t>
+          <t>40,34; 571,25</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 12,7</t>
+          <t>-1,86; 12,89</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,7; -1,23</t>
+          <t>-12,93; -0,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,74; 19,78</t>
+          <t>6,97; 20,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 11,44</t>
+          <t>-0,26; 11,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 6,23</t>
+          <t>-5,99; 6,04</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,38; 23,79</t>
+          <t>12,77; 23,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,8; 10,09</t>
+          <t>0,61; 10,15</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 1,81</t>
+          <t>-7,12; 1,64</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,33; 20,34</t>
+          <t>12,27; 20,42</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 108,66</t>
+          <t>-11,21; 110,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-66,7; -7,03</t>
+          <t>-65,93; -2,19</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34,86; 165,4</t>
+          <t>36,72; 179,62</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 82,08</t>
+          <t>-2,56; 84,41</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,51; 43,58</t>
+          <t>-29,28; 42,64</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>62,57; 176,09</t>
+          <t>57,38; 173,56</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,14; 71,85</t>
+          <t>3,61; 71,56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 13,62</t>
+          <t>-36,53; 11,02</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>62,75; 149,51</t>
+          <t>63,77; 148,29</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,3</t>
+          <t>1,46; 4,22</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,73</t>
+          <t>-1,02; 1,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,03</t>
+          <t>3,16; 8,11</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,86</t>
+          <t>2,08; 4,94</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,09</t>
+          <t>-0,7; 2,16</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,29; 24,61</t>
+          <t>5,37; 25,2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,16</t>
+          <t>2,26; 4,15</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,41</t>
+          <t>-0,44; 1,6</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,6; 20,5</t>
+          <t>5,62; 18,78</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>20,37; 70,69</t>
+          <t>19,79; 70,89</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 28,49</t>
+          <t>-13,91; 25,86</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>47,85; 127,85</t>
+          <t>48,36; 132,68</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22,41; 65,67</t>
+          <t>23,38; 67,25</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 28,79</t>
+          <t>-8,54; 28,77</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>64,3; 322,65</t>
+          <t>63,86; 312,37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,81; 60,41</t>
+          <t>28,79; 60,26</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 20,43</t>
+          <t>-5,7; 22,29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>74,06; 262,23</t>
+          <t>75,31; 258,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,9</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>4,94</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,58</t>
+          <t>0,07; 4,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 4,41</t>
+          <t>-0,32; 4,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 8,66</t>
+          <t>1,23; 8,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,37</t>
+          <t>-1,09; 4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,74</t>
+          <t>-3,83; 1,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 10,54</t>
+          <t>1,64; 11,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,83</t>
+          <t>0,23; 3,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,83</t>
+          <t>-1,31; 2,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,76</t>
+          <t>2,28; 8,2</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192,71%</t>
+          <t>208,96%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>131,21%</t>
+          <t>145,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>147,88%</t>
+          <t>166,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 368,36</t>
+          <t>-7,71; 418,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 367,83</t>
+          <t>-20,14; 340,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 628,75</t>
+          <t>23,71; 735,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 163,0</t>
+          <t>-23,54; 169,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,39; 34,57</t>
+          <t>-71,58; 41,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,79; 354,63</t>
+          <t>27,63; 376,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 176,81</t>
+          <t>1,76; 175,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,15; 77,94</t>
+          <t>-36,6; 93,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,41; 318,61</t>
+          <t>59,19; 348,56</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,1</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,23</t>
+          <t>5,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,08</t>
+          <t>0,57; 5,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,52</t>
+          <t>-1,7; 2,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 12,8</t>
+          <t>3,74; 12,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,61</t>
+          <t>0,58; 5,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,66</t>
+          <t>-1,54; 2,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 6,25</t>
+          <t>1,04; 6,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,62</t>
+          <t>1,38; 4,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,89</t>
+          <t>-1,12; 1,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,07</t>
+          <t>3,05; 8,15</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>237,47%</t>
+          <t>215,85%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>119,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>159,32%</t>
+          <t>166,9%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 201,65</t>
+          <t>10,61; 204,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,09; 107,55</t>
+          <t>-40,77; 95,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,78; 489,2</t>
+          <t>85,68; 456,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,64; 248,31</t>
+          <t>8,78; 239,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 126,56</t>
+          <t>-40,06; 129,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 284,03</t>
+          <t>19,39; 285,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,75; 174,56</t>
+          <t>31,44; 167,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 74,95</t>
+          <t>-28,75; 65,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64,64; 287,5</t>
+          <t>75,13; 289,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,1</t>
+          <t>-0,65; 4,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,89</t>
+          <t>-3,09; 1,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 3,51</t>
+          <t>-2,11; 3,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,45</t>
+          <t>0,41; 6,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,82</t>
+          <t>-3,24; 1,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,45</t>
+          <t>-0,3; 5,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,79</t>
+          <t>0,68; 4,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,08</t>
+          <t>-2,54; 1,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,31</t>
+          <t>-0,53; 3,3</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 129,44</t>
+          <t>-10,7; 132,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 54,46</t>
+          <t>-46,9; 50,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 98,47</t>
+          <t>-32,53; 85,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 128,92</t>
+          <t>4,12; 127,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 40,84</t>
+          <t>-43,05; 33,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 90,27</t>
+          <t>-5,36; 107,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,85; 99,95</t>
+          <t>9,17; 98,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,79; 21,61</t>
+          <t>-38,77; 23,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 71,22</t>
+          <t>-8,23; 67,57</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>4,43</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,97</t>
+          <t>-0,58; 5,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 6,25</t>
+          <t>-0,54; 6,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 8,89</t>
+          <t>3,58; 10,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 5,45</t>
+          <t>-2,09; 6,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 0,98</t>
+          <t>-6,15; 0,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 4,29</t>
+          <t>-1,65; 5,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,86</t>
+          <t>-0,29; 4,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,54</t>
+          <t>-2,62; 2,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 5,33</t>
+          <t>2,06; 6,79</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>101,92%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 109,16</t>
+          <t>-7,86; 107,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 118,46</t>
+          <t>-7,12; 112,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 144,11</t>
+          <t>37,71; 193,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 64,04</t>
+          <t>-17,66; 68,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,12; 12,68</t>
+          <t>-47,56; 7,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 48,04</t>
+          <t>-12,72; 61,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 64,0</t>
+          <t>-3,11; 66,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 33,07</t>
+          <t>-25,71; 32,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,57; 66,29</t>
+          <t>20,22; 91,98</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>4,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 5,44</t>
+          <t>-4,21; 5,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,64</t>
+          <t>-6,21; 2,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 10,92</t>
+          <t>1,44; 10,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 9,21</t>
+          <t>-0,51; 8,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 9,1</t>
+          <t>0,67; 9,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 6,41</t>
+          <t>-1,06; 6,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,02</t>
+          <t>-0,98; 5,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,86</t>
+          <t>-1,54; 4,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,44</t>
+          <t>1,6; 7,58</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 54,72</t>
+          <t>-28,02; 49,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,76; 29,07</t>
+          <t>-41,33; 25,99</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8,88; 107,6</t>
+          <t>9,62; 113,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 118,63</t>
+          <t>-5,4; 112,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,63; 115,94</t>
+          <t>5,09; 125,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 84,19</t>
+          <t>-9,61; 90,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 61,72</t>
+          <t>-7,26; 58,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 53,49</t>
+          <t>-12,2; 49,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,08; 79,82</t>
+          <t>11,87; 78,03</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,41</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23,29</t>
+          <t>5,92</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 9,65</t>
+          <t>-1,6; 9,73</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 2,73</t>
+          <t>-7,25; 2,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,29; 9,47</t>
+          <t>0,23; 9,69</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 8,01</t>
+          <t>-2,84; 7,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,81</t>
+          <t>-3,46; 5,7</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,5; 67,71</t>
+          <t>2,66; 10,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 7,2</t>
+          <t>-0,45; 7,1</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 2,95</t>
+          <t>-3,31; 3,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,84; 53,52</t>
+          <t>2,67; 8,92</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>310,73%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>204,87%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 101,98</t>
+          <t>-12,8; 99,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 30,55</t>
+          <t>-49,45; 25,96</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 102,66</t>
+          <t>0,15; 105,1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 93,39</t>
+          <t>-21,64; 86,82</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 66,82</t>
+          <t>-27,59; 62,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44,34; 764,07</t>
+          <t>19,47; 128,48</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 72,72</t>
+          <t>-5,7; 69,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 30,39</t>
+          <t>-25,98; 33,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>40,34; 571,25</t>
+          <t>20,2; 94,62</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>12,9</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,69</t>
+          <t>18,79</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16,55</t>
+          <t>16,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 12,89</t>
+          <t>-2,04; 12,74</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-12,93; -0,7</t>
+          <t>-12,64; -0,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,97; 20,06</t>
+          <t>5,92; 19,18</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 11,67</t>
+          <t>-1,16; 11,91</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 6,04</t>
+          <t>-6,14; 6,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,77; 23,65</t>
+          <t>13,12; 23,93</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,61; 10,15</t>
+          <t>0,65; 10,1</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 1,64</t>
+          <t>-6,4; 2,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12,27; 20,42</t>
+          <t>12,28; 20,69</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>109,24%</t>
+          <t>109,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>100,62%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 110,18</t>
+          <t>-14,8; 100,03</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,93; -2,19</t>
+          <t>-64,87; -3,5</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>36,72; 179,62</t>
+          <t>29,5; 158,09</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 84,41</t>
+          <t>-6,32; 90,13</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 42,64</t>
+          <t>-31,51; 46,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>57,38; 173,56</t>
+          <t>60,94; 175,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,61; 71,56</t>
+          <t>3,27; 71,54</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 11,02</t>
+          <t>-35,38; 15,87</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>63,77; 148,29</t>
+          <t>63,45; 155,02</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,54</t>
+          <t>6,46</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>6,67</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,22</t>
+          <t>1,45; 4,24</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,57</t>
+          <t>-0,89; 1,7</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,11</t>
+          <t>5,36; 8,39</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,94</t>
+          <t>2,02; 4,96</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,16</t>
+          <t>-0,57; 2,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,37; 25,2</t>
+          <t>5,06; 7,77</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,15</t>
+          <t>2,17; 4,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,6</t>
+          <t>-0,39; 1,48</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,62; 18,78</t>
+          <t>5,63; 7,76</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>103,25%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>131,01%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>114,93%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>19,79; 70,89</t>
+          <t>19,54; 68,27</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 25,86</t>
+          <t>-12,17; 27,67</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>48,36; 132,68</t>
+          <t>72,44; 139,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>23,38; 67,25</t>
+          <t>22,48; 65,7</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 28,77</t>
+          <t>-6,88; 27,78</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>63,86; 312,37</t>
+          <t>56,08; 105,59</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,79; 60,26</t>
+          <t>27,61; 59,31</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 22,29</t>
+          <t>-5,01; 21,55</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>75,31; 258,01</t>
+          <t>71,56; 113,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
